--- a/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>-0.01</v>
+        <v>0.01743858990883105</v>
       </c>
       <c r="I6" s="22">
         <f>B95</f>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>-0.005</v>
+        <v>0.02243858990883105</v>
       </c>
       <c r="I7" s="22">
         <f>B144</f>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>0</v>
+        <v>0.02743858990883105</v>
       </c>
       <c r="I8" s="22">
         <f>B193</f>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>0.005</v>
+        <v>0.03243858990883105</v>
       </c>
       <c r="I9" s="22">
         <f>B242</f>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>0.01</v>
+        <v>0.03743858990883105</v>
       </c>
       <c r="I10" s="22">
         <f>B291</f>
@@ -42359,7 +42359,7 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Levers for this block — the base case sets them all neutral</t>
+          <t>Levers for this block — neutral except the adopted base-period correction on row 7</t>
         </is>
       </c>
       <c r="B5" s="13" t="n"/>
@@ -42384,11 +42384,11 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Gross-margin shift</t>
+          <t>Gross-margin shift — the adopted base-period correction</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>0</v>
+        <v>0.02743858990883105</v>
       </c>
     </row>
     <row r="8">

--- a/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>0.951</v>
@@ -2270,19 +2270,19 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>7.709561159148157</v>
+        <v>7.725762121511933</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8.598972959864378</v>
+        <v>8.622147295622389</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>9.170972589675991</v>
+        <v>9.17108007035451</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>9.785586992007069</v>
+        <v>9.755276306169151</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>10.91362189019824</v>
+        <v>10.8842084723336</v>
       </c>
     </row>
     <row r="15">
@@ -2292,19 +2292,19 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>6.901709500909541</v>
+        <v>6.937402104405309</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>8.344230883407748</v>
+        <v>8.385426149926493</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>9.329430138739404</v>
+        <v>9.328271049604574</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>10.41934979174632</v>
+        <v>10.37679624330905</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>12.60453843225594</v>
+        <v>12.52442131892482</v>
       </c>
     </row>
     <row r="17">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="B22" s="31" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8235294117647058</v>
       </c>
     </row>
     <row r="23">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="B24" s="28" t="n">
-        <v>0.4612000000000001</v>
+        <v>0.4516500000000001</v>
       </c>
     </row>
     <row r="26" ht="33" customHeight="1">
@@ -39249,7 +39249,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39274,7 +39274,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39299,7 +39299,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39324,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39349,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39374,7 +39374,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39399,7 +39399,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39424,7 +39424,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39449,7 +39449,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39474,7 +39474,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39499,7 +39499,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39524,7 +39524,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39549,7 +39549,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39574,7 +39574,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39624,7 +39624,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39649,7 +39649,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39674,7 +39674,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39699,7 +39699,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39724,7 +39724,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39749,7 +39749,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39774,7 +39774,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39799,7 +39799,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39824,7 +39824,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39849,7 +39849,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39874,7 +39874,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39899,7 +39899,7 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39924,7 +39924,7 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39949,7 +39949,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39974,7 +39974,7 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -39999,7 +39999,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40024,7 +40024,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40074,7 +40074,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40099,7 +40099,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40124,7 +40124,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40149,7 +40149,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40174,7 +40174,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40199,7 +40199,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. A figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>

--- a/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
@@ -2759,7 +2759,7 @@
         <v>0.24556</v>
       </c>
       <c r="G27" s="29" t="n">
-        <v>0.143982185805472</v>
+        <v>0.1304821858054719</v>
       </c>
       <c r="I27" s="22">
         <f>B830</f>
@@ -2776,7 +2776,7 @@
         <v>0.26438</v>
       </c>
       <c r="G28" s="29" t="n">
-        <v>0.156582185805472</v>
+        <v>0.143082185805472</v>
       </c>
       <c r="I28" s="22">
         <f>B879</f>
@@ -2793,7 +2793,7 @@
         <v>0.2743872044180305</v>
       </c>
       <c r="G29" s="29" t="n">
-        <v>0.1632820144806677</v>
+        <v>0.1497820144806677</v>
       </c>
       <c r="I29" s="22">
         <f>B928</f>
@@ -2814,7 +2814,7 @@
         <v>0.297315</v>
       </c>
       <c r="G30" s="29" t="n">
-        <v>0.178632185805472</v>
+        <v>0.165132185805472</v>
       </c>
       <c r="I30" s="22">
         <f>B977</f>
@@ -2831,7 +2831,7 @@
         <v>0.31143</v>
       </c>
       <c r="G31" s="29" t="n">
-        <v>0.188082185805472</v>
+        <v>0.174582185805472</v>
       </c>
       <c r="I31" s="22">
         <f>B1026</f>
@@ -35772,14 +35772,14 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1.663882692390205</v>
+        <v>1.654937895576095</v>
       </c>
       <c r="C6" s="9">
         <f>'Fundamental Valuation'!B10</f>
         <v/>
       </c>
       <c r="D6" s="8" t="n">
-        <v>27.51811494973379</v>
+        <v>31.26743275868161</v>
       </c>
       <c r="E6" s="10">
         <f>Assumptions!$B$189</f>
@@ -35835,14 +35835,14 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>5.026420658497639</v>
+        <v>5.271071104859923</v>
       </c>
       <c r="C9" s="9">
         <f>'Fundamental Valuation'!E13</f>
         <v/>
       </c>
       <c r="D9" s="8" t="n">
-        <v>7.672753838280063</v>
+        <v>8.154190522944409</v>
       </c>
       <c r="E9" s="10">
         <f>Assumptions!$B$192</f>
@@ -36140,7 +36140,7 @@
         <v/>
       </c>
       <c r="C13" s="24">
-        <f>0.2170207072</f>
+        <f>0.2083403653</f>
         <v/>
       </c>
       <c r="D13" s="20">
@@ -40547,7 +40547,7 @@
         </is>
       </c>
       <c r="B180" s="29" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
